--- a/docs/Files/Small-format_model/ODYM_Classifications_SF.xlsx
+++ b/docs/Files/Small-format_model/ODYM_Classifications_SF.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6FF8C3F-489D-42C6-81E8-69F80097D9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F446BC-B3B8-467B-8AC6-EEC74723DAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover_Dimensions_Aspects" sheetId="8" r:id="rId1"/>
@@ -869,12 +869,6 @@
     <t>LIB materials</t>
   </si>
   <si>
-    <t>EV LIB</t>
-  </si>
-  <si>
-    <t>other EV LIB products</t>
-  </si>
-  <si>
     <t>LIB scrap</t>
   </si>
   <si>
@@ -885,6 +879,12 @@
   </si>
   <si>
     <t>ODYM_Classifications_SF</t>
+  </si>
+  <si>
+    <t>SF LIB</t>
+  </si>
+  <si>
+    <t>other SF LIB products</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.35">
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
@@ -1812,10 +1812,10 @@
         <v>275</v>
       </c>
       <c r="F11" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" t="s">
         <v>277</v>
-      </c>
-      <c r="G11" t="s">
-        <v>279</v>
       </c>
       <c r="H11" t="str">
         <f>'10_Regions'!D2</f>
@@ -1842,10 +1842,10 @@
         <v>276</v>
       </c>
       <c r="F12" t="s">
+        <v>282</v>
+      </c>
+      <c r="G12" t="s">
         <v>278</v>
-      </c>
-      <c r="G12" t="s">
-        <v>280</v>
       </c>
       <c r="I12" t="str">
         <f>Scenario!D3</f>
@@ -26391,7 +26391,7 @@
         <v>224</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -26406,7 +26406,7 @@
         <v>239</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -26577,7 +26577,7 @@
         <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>240</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E3">
         <v>1</v>
